--- a/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -323,7 +323,7 @@
     <t>DocumentReference.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="513">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -834,7 +834,88 @@
     <t>DocumentEntry.author</t>
   </si>
   <si>
-    <t>DocumentReference.author.id</t>
+    <t>DocumentReference.authenticator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+</t>
+  </si>
+  <si>
+    <t>Who/what authenticated the document</t>
+  </si>
+  <si>
+    <t>Which person or organization authenticates that this document is valid.</t>
+  </si>
+  <si>
+    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
+  </si>
+  <si>
+    <t>Composition.attester</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="AUTHEN"].role[classCode="ASSIGNED"]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/legalAuthenticator</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>TXA-10</t>
+  </si>
+  <si>
+    <t>DocumentEntry.legalAuthenticator</t>
+  </si>
+  <si>
+    <t>DocumentReference.custodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+</t>
+  </si>
+  <si>
+    <t>Organization which maintains the document</t>
+  </si>
+  <si>
+    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
+  </si>
+  <si>
+    <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
+  </si>
+  <si>
+    <t>Composition.custodian</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="RCV"].role[classCode="CUST"].scoper[classCode="ORG" and determinerCode="INST"]</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Relationships to other documents</t>
+  </si>
+  <si>
+    <t>Relationships that this document has with other document references that already exist.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
+  </si>
+  <si>
+    <t>Composition.relatesTo</t>
+  </si>
+  <si>
+    <t>.outboundRelationship</t>
+  </si>
+  <si>
+    <t>DocumentEntry Associations</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -853,7 +934,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>DocumentReference.author.extension</t>
+    <t>DocumentReference.relatesTo.extension</t>
   </si>
   <si>
     <t>Additional content defined by implementations</t>
@@ -862,213 +943,7 @@
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.author.extension:context</t>
-  </si>
-  <si>
-    <t>context</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/reference-context}
-</t>
-  </si>
-  <si>
-    <t>Semantic role or contextual meaning of the reference</t>
-  </si>
-  <si>
-    <t>Provides additional semantic qualification for the reference,
-including role, capacity, or contextual purpose.</t>
-  </si>
-  <si>
-    <t>DocumentReference.author.extension:dictationDateTime</t>
-  </si>
-  <si>
-    <t>dictationDateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/documentReference-author-dictationDateTime}
-</t>
-  </si>
-  <si>
-    <t>Date and time the author dictated the document</t>
-  </si>
-  <si>
-    <t>Applied to the author element of a DocumentReference resource. Captures
-the exact date and time when the author dictated the document.
-This information is not available in the standard FHIR DocumentReference
-resource.</t>
-  </si>
-  <si>
-    <t>DocumentReference.author.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>DocumentReference.author.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>DocumentReference.author.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>DocumentReference.author.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
-  </si>
-  <si>
-    <t>DocumentReference.authenticator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
-</t>
-  </si>
-  <si>
-    <t>Who/what authenticated the document</t>
-  </si>
-  <si>
-    <t>Which person or organization authenticates that this document is valid.</t>
-  </si>
-  <si>
-    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
-  </si>
-  <si>
-    <t>Composition.attester</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="AUTHEN"].role[classCode="ASSIGNED"]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/legalAuthenticator</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>TXA-10</t>
-  </si>
-  <si>
-    <t>DocumentEntry.legalAuthenticator</t>
-  </si>
-  <si>
-    <t>DocumentReference.custodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
-</t>
-  </si>
-  <si>
-    <t>Organization which maintains the document</t>
-  </si>
-  <si>
-    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
-  </si>
-  <si>
-    <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
-  </si>
-  <si>
-    <t>Composition.custodian</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="RCV"].role[classCode="CUST"].scoper[classCode="ORG" and determinerCode="INST"]</t>
-  </si>
-  <si>
-    <t>DocumentReference.relatesTo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Relationships to other documents</t>
-  </si>
-  <si>
-    <t>Relationships that this document has with other document references that already exist.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
-  </si>
-  <si>
-    <t>Composition.relatesTo</t>
-  </si>
-  <si>
-    <t>.outboundRelationship</t>
-  </si>
-  <si>
-    <t>DocumentEntry Associations</t>
-  </si>
-  <si>
-    <t>DocumentReference.relatesTo.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.relatesTo.extension</t>
   </si>
   <si>
     <t>DocumentReference.relatesTo.modifierExtension</t>
@@ -1175,6 +1050,9 @@
   </si>
   <si>
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
@@ -1262,6 +1140,9 @@
     <t>DocumentReference.content.attachment.extension</t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>DocumentReference.content.attachment.contentType</t>
   </si>
   <si>
@@ -1526,8 +1407,7 @@
   <si>
     <t>Applied to the context section of a DocumentReference resource. Stores the
 date and time when the clinician dictated the document content — distinct
-from when it was authored, transcribed, or signed.
-Standard FHIR DocumentReference context has no dictation timestamp field.</t>
+from when it was authored, transcribed, or signed.</t>
   </si>
   <si>
     <t>DocumentReference.context.extension:cosigner</t>
@@ -1563,8 +1443,7 @@
   <si>
     <t>Applied to the context section of a DocumentReference resource. Stores the
 date and time when the finalized report was made available or released —
-separate from dictation, transcription, or document creation time.
-Standard FHIR DocumentReference has no report release timestamp field.</t>
+separate from dictation, transcription, or document creation time.</t>
   </si>
   <si>
     <t>DocumentReference.context.modifierExtension</t>
@@ -2060,7 +1939,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ69"/>
+  <dimension ref="A1:AQ61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.01953125" customWidth="true" bestFit="true"/>
@@ -4726,7 +4605,9 @@
       <c r="M22" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="N22" s="2"/>
+      <c r="N22" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4775,7 +4656,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4787,47 +4668,47 @@
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>20</v>
+        <v>268</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>20</v>
+        <v>269</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>20</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4839,16 +4720,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>137</v>
+        <v>273</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>154</v>
+        <v>276</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4886,40 +4767,40 @@
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>20</v>
+        <v>277</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4936,14 +4817,12 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4961,18 +4840,20 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -5021,7 +4902,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5033,16 +4914,16 @@
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>20</v>
+        <v>284</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -5054,19 +4935,17 @@
         <v>20</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>20</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
@@ -5087,13 +4966,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5144,19 +5023,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -5165,7 +5044,7 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -5182,21 +5061,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5205,19 +5084,19 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>285</v>
+        <v>154</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5267,19 +5146,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -5288,7 +5167,7 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>135</v>
+        <v>292</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -5305,44 +5184,46 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5366,13 +5247,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>294</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5390,19 +5271,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -5428,10 +5309,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5439,7 +5320,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>92</v>
@@ -5454,16 +5335,16 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5489,13 +5370,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5513,10 +5394,10 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>92</v>
@@ -5531,10 +5412,10 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -5546,15 +5427,15 @@
         <v>20</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5562,7 +5443,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>92</v>
@@ -5577,17 +5458,15 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>262</v>
+        <v>312</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5636,10 +5515,10 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>92</v>
@@ -5654,10 +5533,10 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>135</v>
+        <v>316</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
@@ -5669,15 +5548,15 @@
         <v>20</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>20</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5697,21 +5576,23 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5759,7 +5640,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5774,33 +5655,33 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5811,7 +5692,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5820,21 +5701,23 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>198</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5858,13 +5741,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5882,13 +5765,13 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
@@ -5897,33 +5780,33 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>20</v>
+        <v>336</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>20</v>
+        <v>338</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5931,13 +5814,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
@@ -5946,17 +5829,15 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>326</v>
+        <v>280</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -6005,10 +5886,10 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>81</v>
@@ -6023,10 +5904,10 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -6038,15 +5919,15 @@
         <v>20</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6069,13 +5950,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6126,7 +6007,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6147,7 +6028,7 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -6164,10 +6045,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6193,10 +6074,10 @@
         <v>137</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>154</v>
@@ -6249,7 +6130,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6270,7 +6151,7 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -6287,14 +6168,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>336</v>
+        <v>298</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6316,10 +6197,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>337</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>338</v>
+        <v>300</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>154</v>
@@ -6374,7 +6255,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6410,12 +6291,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6429,7 +6310,7 @@
         <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
@@ -6438,16 +6319,16 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>112</v>
+        <v>348</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6473,13 +6354,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6497,7 +6378,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>92</v>
@@ -6509,36 +6390,36 @@
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>352</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6546,7 +6427,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>92</v>
@@ -6558,16 +6439,16 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>350</v>
+        <v>288</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>351</v>
+        <v>289</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6618,10 +6499,10 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>349</v>
+        <v>291</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>92</v>
@@ -6630,16 +6511,16 @@
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6651,26 +6532,26 @@
         <v>20</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>355</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6679,23 +6560,21 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>295</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6731,31 +6610,31 @@
         <v>20</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>20</v>
+        <v>359</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>356</v>
+        <v>296</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6764,7 +6643,7 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>361</v>
+        <v>292</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6773,18 +6652,18 @@
         <v>20</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6795,10 +6674,10 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -6807,19 +6686,17 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>198</v>
+        <v>112</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6832,7 +6709,7 @@
         <v>20</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>20</v>
@@ -6844,13 +6721,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6868,13 +6745,13 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -6886,30 +6763,30 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>375</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6917,13 +6794,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G40" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H40" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
@@ -6932,16 +6809,18 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>326</v>
+        <v>112</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6953,7 +6832,7 @@
         <v>20</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>20</v>
@@ -6965,13 +6844,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6989,13 +6868,13 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
@@ -7007,10 +6886,10 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -7025,12 +6904,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7044,7 +6923,7 @@
         <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>20</v>
@@ -7053,16 +6932,20 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>262</v>
+        <v>378</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>263</v>
+        <v>379</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -7110,7 +6993,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>265</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7119,10 +7002,10 @@
         <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>20</v>
+        <v>384</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -7131,7 +7014,7 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>266</v>
+        <v>385</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -7140,52 +7023,54 @@
         <v>20</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>20</v>
+        <v>386</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>137</v>
+        <v>388</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>268</v>
+        <v>389</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>269</v>
+        <v>390</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -7197,7 +7082,7 @@
         <v>20</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>20</v>
@@ -7233,19 +7118,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>271</v>
+        <v>394</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>20</v>
+        <v>384</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -7254,7 +7139,7 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>266</v>
+        <v>395</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -7263,7 +7148,7 @@
         <v>20</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>20</v>
@@ -7271,45 +7156,45 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>137</v>
+        <v>398</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>399</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>400</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>154</v>
+        <v>401</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>155</v>
+        <v>402</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7358,19 +7243,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>339</v>
+        <v>403</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7379,7 +7264,7 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>135</v>
+        <v>404</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -7394,12 +7279,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7407,13 +7292,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
@@ -7422,18 +7307,20 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7481,10 +7368,10 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>92</v>
@@ -7493,36 +7380,36 @@
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>389</v>
+        <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>393</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7542,19 +7429,21 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>263</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>264</v>
+        <v>414</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7566,7 +7455,7 @@
         <v>20</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>20</v>
@@ -7602,7 +7491,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>265</v>
+        <v>417</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7614,7 +7503,7 @@
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7623,7 +7512,7 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>266</v>
+        <v>418</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -7640,21 +7529,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7663,21 +7552,21 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>137</v>
+        <v>420</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>268</v>
+        <v>421</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7713,31 +7602,31 @@
         <v>20</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>271</v>
+        <v>424</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7746,7 +7635,7 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>266</v>
+        <v>404</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7763,10 +7652,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7789,18 +7678,18 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>112</v>
+        <v>426</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7812,7 +7701,7 @@
         <v>20</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>20</v>
@@ -7824,13 +7713,11 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7848,7 +7735,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7866,30 +7753,30 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>20</v>
+        <v>431</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>404</v>
+        <v>343</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>405</v>
+        <v>20</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7903,7 +7790,7 @@
         <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
@@ -7912,18 +7799,18 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>112</v>
+        <v>280</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7935,7 +7822,7 @@
         <v>20</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>20</v>
@@ -7947,13 +7834,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7971,7 +7858,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7992,7 +7879,7 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -8007,12 +7894,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8026,7 +7913,7 @@
         <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
@@ -8035,20 +7922,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>414</v>
+        <v>288</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>415</v>
+        <v>289</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -8096,7 +7979,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>291</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8105,10 +7988,10 @@
         <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -8117,7 +8000,7 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>421</v>
+        <v>292</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -8126,18 +8009,18 @@
         <v>20</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8148,32 +8031,28 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>424</v>
+        <v>137</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>425</v>
+        <v>138</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -8185,7 +8064,7 @@
         <v>20</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>429</v>
+        <v>20</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>20</v>
@@ -8209,31 +8088,29 @@
         <v>20</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>430</v>
+        <v>296</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8242,7 +8119,7 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>431</v>
+        <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -8251,7 +8128,7 @@
         <v>20</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>432</v>
+        <v>20</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>20</v>
@@ -8259,12 +8136,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>20</v>
       </c>
@@ -8282,23 +8161,19 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
@@ -8346,19 +8221,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>439</v>
+        <v>296</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -8367,7 +8242,7 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>440</v>
+        <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>20</v>
@@ -8384,12 +8259,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>20</v>
       </c>
@@ -8407,23 +8284,19 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -8471,19 +8344,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>446</v>
+        <v>296</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8492,7 +8365,7 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>447</v>
+        <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -8509,12 +8382,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8532,21 +8407,19 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>262</v>
+        <v>453</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>451</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8558,7 +8431,7 @@
         <v>20</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>452</v>
+        <v>20</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>20</v>
@@ -8594,19 +8467,19 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>453</v>
+        <v>296</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8615,7 +8488,7 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>454</v>
+        <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -8632,43 +8505,45 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>456</v>
+        <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>457</v>
+        <v>299</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>459</v>
+        <v>155</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8717,19 +8592,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>301</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8738,7 +8613,7 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>135</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8755,10 +8630,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8778,20 +8653,18 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8816,11 +8689,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>466</v>
+        <v>20</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8838,13 +8713,13 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
@@ -8853,33 +8728,33 @@
         <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>20</v>
+        <v>461</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>380</v>
+        <v>463</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>468</v>
+        <v>20</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>20</v>
+        <v>464</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>469</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8890,28 +8765,28 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>326</v>
+        <v>198</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8937,13 +8812,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>20</v>
+        <v>469</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>20</v>
+        <v>470</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -8961,13 +8836,13 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
@@ -8979,30 +8854,30 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>20</v>
+        <v>471</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AN56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9016,22 +8891,22 @@
         <v>92</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>262</v>
+        <v>475</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>263</v>
+        <v>476</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>264</v>
+        <v>477</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9082,7 +8957,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>265</v>
+        <v>474</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9094,19 +8969,19 @@
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>20</v>
+        <v>478</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>266</v>
+        <v>479</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>20</v>
+        <v>480</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -9115,15 +8990,15 @@
         <v>20</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>20</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9134,7 +9009,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -9146,13 +9021,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>138</v>
+        <v>483</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>139</v>
+        <v>484</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9179,53 +9054,55 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>20</v>
+        <v>485</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>20</v>
+        <v>486</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>271</v>
+        <v>482</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>20</v>
+        <v>487</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>20</v>
+        <v>488</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>20</v>
+        <v>489</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9234,19 +9111,17 @@
         <v>20</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>20</v>
+        <v>490</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>20</v>
       </c>
@@ -9267,16 +9142,20 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>479</v>
+        <v>198</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
       </c>
@@ -9300,13 +9179,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>20</v>
+        <v>496</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>20</v>
+        <v>497</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9324,31 +9203,31 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>271</v>
+        <v>491</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>20</v>
+        <v>487</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>20</v>
+        <v>488</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>20</v>
+        <v>487</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9357,19 +9236,17 @@
         <v>20</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>20</v>
+        <v>498</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>20</v>
       </c>
@@ -9390,13 +9267,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9447,31 +9324,31 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9480,19 +9357,17 @@
         <v>20</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>20</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>20</v>
       </c>
@@ -9501,7 +9376,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9513,15 +9388,17 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9570,7 +9447,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>271</v>
+        <v>504</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9579,22 +9456,22 @@
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>20</v>
+        <v>509</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>20</v>
+        <v>510</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>20</v>
+        <v>511</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9603,991 +9480,11 @@
         <v>20</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="L65" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>548</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ69">
+  <autoFilter ref="A1:AQ61">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10597,7 +9494,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -737,7 +737,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Practitioner|Group|Device) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -803,7 +803,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson|Device) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -837,7 +837,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -871,7 +871,7 @@
     <t>DocumentReference.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -993,7 +993,7 @@
     <t>DocumentReference.relatesTo.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/documentreference-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1452,7 +1452,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1584,7 +1584,7 @@
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1600,7 +1600,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Resource|http://314e.com/fhir/StructureDefinition/account-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e|http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/contract-314e|http://314e.com/fhir/StructureDefinition/coverage-314e|http://314e.com/fhir/StructureDefinition/detectedissue-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/endpoint-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e|http://314e.com/fhir/StructureDefinition/goal-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/immunizationevaluation-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e|http://314e.com/fhir/StructureDefinition/schedule-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/slot-314e|http://314e.com/fhir/StructureDefinition/specimen-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-documentreference-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>314e-constrained DocumentReference profile derived from QI-Core DocumentReference.
+    <t>314e-constrained DocumentReference profile derived from US Core DocumentReference.
 This profile applies 314e-defined extensions and uses 314e datatype profiles
 where applicable.</t>
   </si>
@@ -464,6 +464,27 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DocumentReference.extension:cosigner</t>
+  </si>
+  <si>
+    <t>cosigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/resource-cosigner}
+</t>
+  </si>
+  <si>
+    <t>Individual who co-signed or verified this document</t>
+  </si>
+  <si>
+    <t>Identifies an individual who reviewed, verified, or co-signed the associated
+clinical document, note, order, or healthcare record, alongside the primary author or requester.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>DocumentReference.extension:additionalInfo</t>
@@ -484,10 +505,6 @@
 represented by the core FHIR elements or existing profiles.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>DocumentReference.modifierExtension</t>
   </si>
   <si>
@@ -1408,24 +1425,6 @@
     <t>Applied to the context section of a DocumentReference resource. Stores the
 date and time when the clinician dictated the document content — distinct
 from when it was authored, transcribed, or signed.</t>
-  </si>
-  <si>
-    <t>DocumentReference.context.extension:cosigner</t>
-  </si>
-  <si>
-    <t>cosigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/documentReference-context-cosigner}
-</t>
-  </si>
-  <si>
-    <t>Co-signer of the document</t>
-  </si>
-  <si>
-    <t>Applied to the context section of a DocumentReference resource. Captures the
-co-signer of the document — a person who has jointly signed or authenticated
-the document alongside the primary author.</t>
   </si>
   <si>
     <t>DocumentReference.context.extension:reportDateTime</t>
@@ -3113,7 +3112,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -3223,11 +3222,13 @@
         <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3240,26 +3241,22 @@
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>155</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
       </c>
@@ -3307,7 +3304,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3316,7 +3313,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>143</v>
@@ -3328,7 +3325,7 @@
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>20</v>
@@ -3345,45 +3342,45 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3432,48 +3429,48 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3484,10 +3481,10 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>20</v>
@@ -3496,16 +3493,20 @@
         <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
       </c>
@@ -3553,13 +3554,13 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -3568,33 +3569,33 @@
         <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AM13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AP13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AQ13" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AQ13" t="s" s="2">
-        <v>176</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3602,32 +3603,30 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>180</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3652,11 +3651,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3674,13 +3675,13 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
@@ -3689,33 +3690,33 @@
         <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3723,16 +3724,16 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>93</v>
@@ -3741,13 +3742,13 @@
         <v>112</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3773,13 +3774,11 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3797,10 +3796,10 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>92</v>
@@ -3812,33 +3811,33 @@
         <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3846,13 +3845,13 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
@@ -3861,16 +3860,16 @@
         <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>198</v>
+        <v>112</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3896,13 +3895,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3920,7 +3919,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3935,44 +3934,44 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>93</v>
@@ -3984,16 +3983,16 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4019,35 +4018,37 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
@@ -4056,49 +4057,47 @@
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -4107,16 +4106,16 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4142,31 +4141,29 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4184,44 +4181,46 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
@@ -4230,15 +4229,17 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>231</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4263,13 +4264,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -4287,13 +4288,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -4302,41 +4303,41 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>233</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>92</v>
@@ -4351,17 +4352,15 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4410,7 +4409,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4425,44 +4424,44 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>20</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>93</v>
@@ -4474,16 +4473,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4533,13 +4532,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4548,33 +4547,33 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
-      <c r="A22" t="s" s="2">
-        <v>261</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4585,28 +4584,28 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4656,13 +4655,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -4671,33 +4670,33 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4720,16 +4719,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4779,7 +4778,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4794,33 +4793,33 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>20</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4831,7 +4830,7 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4840,19 +4839,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4902,13 +4901,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4917,13 +4916,13 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4935,15 +4934,15 @@
         <v>20</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4954,7 +4953,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4963,18 +4962,20 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5023,59 +5024,59 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5087,7 +5088,7 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>137</v>
+        <v>293</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>294</v>
@@ -5095,9 +5096,7 @@
       <c r="M26" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5152,13 +5151,13 @@
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -5167,7 +5166,7 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -5184,14 +5183,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>298</v>
+        <v>156</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5204,10 +5203,10 @@
         <v>20</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>137</v>
@@ -5219,11 +5218,9 @@
         <v>300</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5292,7 +5289,7 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>135</v>
+        <v>297</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
@@ -5316,37 +5313,39 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5370,52 +5369,52 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AG28" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>309</v>
+        <v>135</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -5427,15 +5426,15 @@
         <v>20</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5458,15 +5457,17 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>312</v>
+        <v>112</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5491,13 +5492,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5515,7 +5516,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>92</v>
@@ -5533,30 +5534,30 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5564,7 +5565,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>92</v>
@@ -5579,20 +5580,16 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5640,10 +5637,10 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>92</v>
@@ -5658,10 +5655,10 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
@@ -5670,18 +5667,18 @@
         <v>20</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5692,7 +5689,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5704,19 +5701,19 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>198</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O31" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5741,13 +5738,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5765,13 +5762,13 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
@@ -5783,30 +5780,30 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>334</v>
+        <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5814,13 +5811,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
@@ -5829,16 +5826,20 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>280</v>
+        <v>203</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5862,13 +5863,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>20</v>
+        <v>336</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5886,10 +5887,10 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>81</v>
@@ -5904,25 +5905,25 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AQ32" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AN32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>344</v>
       </c>
@@ -5935,28 +5936,28 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>345</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6007,28 +6008,28 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>344</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>292</v>
+        <v>348</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -6045,21 +6046,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6071,7 +6072,7 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>137</v>
+        <v>293</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>294</v>
@@ -6079,9 +6080,7 @@
       <c r="M34" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6136,13 +6135,13 @@
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -6151,7 +6150,7 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -6168,14 +6167,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>298</v>
+        <v>156</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6188,10 +6187,10 @@
         <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>137</v>
@@ -6203,11 +6202,9 @@
         <v>300</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -6276,7 +6273,7 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>135</v>
+        <v>297</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -6291,46 +6288,48 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I36" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>348</v>
+        <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6378,48 +6377,48 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AK36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="37" hidden="true">
-      <c r="A37" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6427,30 +6426,32 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>288</v>
+        <v>353</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>289</v>
+        <v>354</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6499,10 +6500,10 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>92</v>
@@ -6511,47 +6512,47 @@
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>292</v>
+        <v>348</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>20</v>
+        <v>359</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>20</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6563,7 +6564,7 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>137</v>
+        <v>293</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>294</v>
@@ -6571,9 +6572,7 @@
       <c r="M38" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6610,16 +6609,16 @@
         <v>20</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>296</v>
@@ -6628,13 +6627,13 @@
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6643,7 +6642,7 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6658,46 +6657,46 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>361</v>
+        <v>299</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6709,84 +6708,84 @@
         <v>20</v>
       </c>
       <c r="T39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC39" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="U39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y39" t="s" s="2">
+      <c r="AD39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" hidden="true">
-      <c r="A40" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6800,7 +6799,7 @@
         <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
@@ -6812,14 +6811,14 @@
         <v>112</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6832,7 +6831,7 @@
         <v>20</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>20</v>
@@ -6844,13 +6843,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>117</v>
+        <v>370</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>118</v>
+        <v>371</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6868,7 +6867,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6889,7 +6888,7 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6898,18 +6897,18 @@
         <v>20</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6923,28 +6922,26 @@
         <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K41" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6957,7 +6954,7 @@
         <v>20</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>20</v>
@@ -6969,13 +6966,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6993,7 +6990,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7002,7 +6999,7 @@
         <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>104</v>
@@ -7014,7 +7011,7 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -7023,7 +7020,7 @@
         <v>20</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>20</v>
@@ -7031,10 +7028,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7054,22 +7051,22 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7082,7 +7079,7 @@
         <v>20</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>393</v>
+        <v>20</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>20</v>
@@ -7118,7 +7115,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7127,7 +7124,7 @@
         <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>104</v>
@@ -7139,7 +7136,7 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -7148,18 +7145,18 @@
         <v>20</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7173,7 +7170,7 @@
         <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
@@ -7182,19 +7179,19 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7207,7 +7204,7 @@
         <v>20</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>20</v>
+        <v>398</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>20</v>
@@ -7243,7 +7240,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7252,7 +7249,7 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>20</v>
+        <v>389</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
@@ -7264,7 +7261,7 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -7273,7 +7270,7 @@
         <v>20</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>20</v>
@@ -7281,10 +7278,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7307,19 +7304,19 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7368,7 +7365,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7389,7 +7386,7 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -7406,10 +7403,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7432,17 +7429,19 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>288</v>
+        <v>383</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7455,7 +7454,7 @@
         <v>20</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>416</v>
+        <v>20</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>20</v>
@@ -7491,7 +7490,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7512,7 +7511,7 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -7529,10 +7528,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7555,17 +7554,17 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>420</v>
+        <v>293</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7578,7 +7577,7 @@
         <v>20</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>20</v>
+        <v>421</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>20</v>
@@ -7614,7 +7613,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7635,7 +7634,7 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7650,12 +7649,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7669,7 +7668,7 @@
         <v>92</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
@@ -7678,18 +7677,18 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N47" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7713,11 +7712,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7735,7 +7736,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7753,13 +7754,13 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>431</v>
+        <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>343</v>
+        <v>409</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>432</v>
+        <v>20</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7768,15 +7769,15 @@
         <v>20</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>433</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7799,16 +7800,16 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>280</v>
+        <v>431</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7834,13 +7835,11 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>20</v>
+        <v>435</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7858,7 +7857,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7876,25 +7875,25 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>20</v>
+        <v>436</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AN48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>439</v>
       </c>
@@ -7913,24 +7912,26 @@
         <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>289</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7979,7 +7980,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>291</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7991,7 +7992,7 @@
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -8000,7 +8001,7 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>292</v>
+        <v>443</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -8017,10 +8018,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8031,7 +8032,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -8043,13 +8044,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>137</v>
+        <v>293</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>138</v>
+        <v>294</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>139</v>
+        <v>295</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8088,14 +8089,16 @@
         <v>20</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>296</v>
@@ -8104,13 +8107,13 @@
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8119,7 +8122,7 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -8136,14 +8139,12 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>20</v>
       </c>
@@ -8152,7 +8153,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8164,13 +8165,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>443</v>
+        <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>444</v>
+        <v>138</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>445</v>
+        <v>139</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8209,19 +8210,17 @@
         <v>20</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8230,7 +8229,7 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>143</v>
@@ -8262,7 +8261,7 @@
         <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>447</v>
@@ -8344,7 +8343,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8385,7 +8384,7 @@
         <v>451</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>452</v>
@@ -8467,7 +8466,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8512,7 +8511,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8534,16 +8533,16 @@
         <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8592,7 +8591,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8777,7 +8776,7 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>466</v>
@@ -8812,7 +8811,7 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Y56" t="s" s="2">
         <v>469</v>
@@ -9021,7 +9020,7 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>483</v>
@@ -9054,7 +9053,7 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>485</v>
@@ -9142,7 +9141,7 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>492</v>
@@ -9179,7 +9178,7 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Y59" t="s" s="2">
         <v>496</v>
@@ -9342,13 +9341,13 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
